--- a/tools/Polhem.Definition.Spreadsheet/Templates/FormSchema.zh-TW.xlsx
+++ b/tools/Polhem.Definition.Spreadsheet/Templates/FormSchema.zh-TW.xlsx
@@ -411,7 +411,7 @@
     <x:t>MaxLength</x:t>
   </x:si>
   <x:si>
-    <x:t>文字欄位的長度上限；空白使用預設。</x:t>
+    <x:t>String 欄位的長度上限。會建成資料表欄位時必填，沒填會無法匯入。</x:t>
   </x:si>
   <x:si>
     <x:t>必填</x:t>

--- a/tools/Polhem.Definition.Spreadsheet/Templates/FormSchema.zh-TW.xlsx
+++ b/tools/Polhem.Definition.Spreadsheet/Templates/FormSchema.zh-TW.xlsx
@@ -2374,11 +2374,11 @@
     <x:col min="14" max="15" width="28.710625" style="0" customWidth="1"/>
     <x:col min="16" max="17" width="14.710625" style="0" customWidth="1"/>
     <x:col min="18" max="18" width="10.710625" style="0" customWidth="1"/>
-    <x:col min="19" max="19" width="14.710625" style="0" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <x:col min="20" max="20" width="24.710625" style="0" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <x:col min="21" max="24" width="14.710625" style="0" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <x:col min="25" max="25" width="28.710625" style="0" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <x:col min="26" max="29" width="14.710625" style="0" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <x:col min="19" max="19" width="14.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <x:col min="20" max="20" width="24.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <x:col min="21" max="24" width="14.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <x:col min="25" max="25" width="28.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <x:col min="26" max="29" width="14.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" spans="1:29">

--- a/tools/Polhem.Definition.Spreadsheet/Templates/FormSchema.zh-TW.xlsx
+++ b/tools/Polhem.Definition.Spreadsheet/Templates/FormSchema.zh-TW.xlsx
@@ -438,7 +438,7 @@
     <x:t>輸入控制項</x:t>
   </x:si>
   <x:si>
-    <x:t>空白依資料型別自動決定。有下拉選項時填 DropDownEdit。</x:t>
+    <x:t>Auto 依資料型別自動決定，空白也視為 Auto。有下拉選項時選 DropDownEdit。</x:t>
   </x:si>
   <x:si>
     <x:t>預設值</x:t>

--- a/tools/Polhem.Definition.Spreadsheet/Templates/FormSchema.zh-TW.xlsx
+++ b/tools/Polhem.Definition.Spreadsheet/Templates/FormSchema.zh-TW.xlsx
@@ -471,7 +471,7 @@
     <x:t>RelationFieldMappings</x:t>
   </x:si>
   <x:si>
-    <x:t>空白時依慣例產生。自訂時寫 來源=目的，以分號分隔，例如 sys_id=ref_customer_id; sys_name=ref_customer_name。</x:t>
+    <x:t>空白時依慣例產生。自訂時寫 來源=目的，以分號分隔，例如 sys_id=ref_customer_id; sys_name=ref_customer_name。只在查詢選取時回寫、查詢 JOIN 不讀的對應，在後面加 (lookup)，例如 sales_rowid=sales_rowid (lookup)；只有這類對應時仍會依慣例補上。</x:t>
   </x:si>
   <x:si>
     <x:t>計算公式</x:t>
@@ -531,21 +531,6 @@
     <x:t>NumberFormat</x:t>
   </x:si>
   <x:si>
-    <x:t>查詢表單</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LookupProgId</x:t>
-  </x:si>
-  <x:si>
-    <x:t>查詢帶回欄位</x:t>
-  </x:si>
-  <x:si>
-    <x:t>LookupFieldMappings</x:t>
-  </x:si>
-  <x:si>
-    <x:t>寫 來源=目的，以分號分隔。</x:t>
-  </x:si>
-  <x:si>
     <x:t>顯示欄位</x:t>
   </x:si>
   <x:si>
@@ -760,12 +745,6 @@
   </x:si>
   <x:si>
     <x:t>{{Fields.CurrencyField}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{Fields.LookupProgId}}</x:t>
-  </x:si>
-  <x:si>
-    <x:t>{{Fields.LookupFieldMappings}}</x:t>
   </x:si>
   <x:si>
     <x:t>{{Fields.DisplayFields}}</x:t>
@@ -1209,7 +1188,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D67"/>
+  <x:dimension ref="A1:D65"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="12.710625" style="0" customWidth="1"/>
@@ -1867,7 +1846,7 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:4">
@@ -1875,10 +1854,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>57</x:v>
@@ -1889,10 +1868,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>57</x:v>
@@ -1900,13 +1879,13 @@
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>57</x:v>
@@ -1914,21 +1893,21 @@
     </x:row>
     <x:row r="58" spans="1:4">
       <x:c r="A58" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
         <x:v>180</x:v>
       </x:c>
-      <x:c r="C58" s="0" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>181</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:4">
       <x:c r="A59" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>182</x:v>
@@ -1937,54 +1916,54 @@
         <x:v>183</x:v>
       </x:c>
       <x:c r="D59" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>184</x:v>
       </x:c>
     </x:row>
     <x:row r="60" spans="1:4">
       <x:c r="A60" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>187</x:v>
       </x:c>
     </x:row>
     <x:row r="61" spans="1:4">
       <x:c r="A61" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>190</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:4">
       <x:c r="A62" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:4">
       <x:c r="A63" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
         <x:v>193</x:v>
@@ -1993,26 +1972,26 @@
         <x:v>194</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:4">
       <x:c r="A64" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
         <x:v>196</x:v>
       </x:c>
-      <x:c r="C64" s="0" t="s">
+      <x:c r="D64" s="0" t="s">
         <x:v>197</x:v>
-      </x:c>
-      <x:c r="D64" s="0" t="s">
-        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:4">
       <x:c r="A65" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>198</x:v>
@@ -2021,34 +2000,6 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:4">
-      <x:c r="A66" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="B66" s="0" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="C66" s="0" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="D66" s="0" t="s">
-        <x:v>202</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:4">
-      <x:c r="A67" s="0" t="s">
-        <x:v>181</x:v>
-      </x:c>
-      <x:c r="B67" s="0" t="s">
-        <x:v>203</x:v>
-      </x:c>
-      <x:c r="C67" s="0" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="D67" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
     </x:row>
@@ -2077,11 +2028,11 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="2" t="s">
-        <x:v>205</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2" t="s">
-        <x:v>206</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
         <x:v>68</x:v>
@@ -2095,7 +2046,7 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>72</x:v>
@@ -2109,7 +2060,7 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>75</x:v>
@@ -2123,7 +2074,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>78</x:v>
@@ -2137,7 +2088,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>80</x:v>
@@ -2151,7 +2102,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>83</x:v>
@@ -2165,7 +2116,7 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>86</x:v>
@@ -2179,7 +2130,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>89</x:v>
@@ -2193,7 +2144,7 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>92</x:v>
@@ -2207,7 +2158,7 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>95</x:v>
@@ -2221,7 +2172,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>98</x:v>
@@ -2235,7 +2186,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
         <x:v>101</x:v>
@@ -2249,7 +2200,7 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>104</x:v>
@@ -2263,7 +2214,7 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>107</x:v>
@@ -2332,16 +2283,16 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>218</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2358,7 +2309,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:AC3"/>
+  <x:dimension ref="A1:AA3"/>
   <x:sheetFormatPr defaultRowHeight="15" outlineLevelCol="1"/>
   <x:cols>
     <x:col min="1" max="1" width="16.710625" style="0" customWidth="1"/>
@@ -2376,12 +2327,10 @@
     <x:col min="18" max="18" width="10.710625" style="0" customWidth="1"/>
     <x:col min="19" max="19" width="14.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
     <x:col min="20" max="20" width="24.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <x:col min="21" max="24" width="14.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <x:col min="25" max="25" width="28.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <x:col min="26" max="29" width="14.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <x:col min="21" max="27" width="14.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:29">
+    <x:row r="1" spans="1:27">
       <x:c r="A1" s="2" t="s">
         <x:v>116</x:v>
       </x:c>
@@ -2458,19 +2407,13 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="Z1" s="4" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="AA1" s="4" t="s">
         <x:v>175</x:v>
       </x:c>
-      <x:c r="AA1" s="4" t="s">
-        <x:v>177</x:v>
-      </x:c>
-      <x:c r="AB1" s="4" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="AC1" s="4" t="s">
-        <x:v>180</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:29" hidden="1">
+    </x:row>
+    <x:row r="2" spans="1:27" hidden="1">
       <x:c r="A2" s="0" t="s">
         <x:v>110</x:v>
       </x:c>
@@ -2547,105 +2490,93 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="Z2" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AA2" s="0" t="s">
-        <x:v>178</x:v>
-      </x:c>
-      <x:c r="AB2" s="0" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="AC2" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:29">
+    <x:row r="3" spans="1:27">
       <x:c r="A3" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
         <x:v>224</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="G3" s="0" t="s">
         <x:v>225</x:v>
       </x:c>
-      <x:c r="C3" s="0" t="s">
+      <x:c r="H3" s="0" t="s">
         <x:v>226</x:v>
       </x:c>
-      <x:c r="D3" s="0" t="s">
+      <x:c r="I3" s="0" t="s">
         <x:v>227</x:v>
       </x:c>
-      <x:c r="E3" s="0" t="s">
+      <x:c r="J3" s="0" t="s">
         <x:v>228</x:v>
       </x:c>
-      <x:c r="F3" s="0" t="s">
+      <x:c r="K3" s="0" t="s">
         <x:v>229</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s">
+      <x:c r="L3" s="0" t="s">
         <x:v>230</x:v>
       </x:c>
-      <x:c r="H3" s="0" t="s">
+      <x:c r="M3" s="0" t="s">
         <x:v>231</x:v>
       </x:c>
-      <x:c r="I3" s="0" t="s">
+      <x:c r="N3" s="0" t="s">
         <x:v>232</x:v>
       </x:c>
-      <x:c r="J3" s="0" t="s">
+      <x:c r="O3" s="0" t="s">
         <x:v>233</x:v>
       </x:c>
-      <x:c r="K3" s="0" t="s">
+      <x:c r="P3" s="0" t="s">
         <x:v>234</x:v>
       </x:c>
-      <x:c r="L3" s="0" t="s">
+      <x:c r="Q3" s="0" t="s">
         <x:v>235</x:v>
       </x:c>
-      <x:c r="M3" s="0" t="s">
+      <x:c r="R3" s="0" t="s">
         <x:v>236</x:v>
       </x:c>
-      <x:c r="N3" s="0" t="s">
+      <x:c r="S3" s="0" t="s">
         <x:v>237</x:v>
       </x:c>
-      <x:c r="O3" s="0" t="s">
+      <x:c r="T3" s="0" t="s">
         <x:v>238</x:v>
       </x:c>
-      <x:c r="P3" s="0" t="s">
+      <x:c r="U3" s="0" t="s">
         <x:v>239</x:v>
       </x:c>
-      <x:c r="Q3" s="0" t="s">
+      <x:c r="V3" s="0" t="s">
         <x:v>240</x:v>
       </x:c>
-      <x:c r="R3" s="0" t="s">
+      <x:c r="W3" s="0" t="s">
         <x:v>241</x:v>
       </x:c>
-      <x:c r="S3" s="0" t="s">
+      <x:c r="X3" s="0" t="s">
         <x:v>242</x:v>
       </x:c>
-      <x:c r="T3" s="0" t="s">
+      <x:c r="Y3" s="0" t="s">
         <x:v>243</x:v>
       </x:c>
-      <x:c r="U3" s="0" t="s">
+      <x:c r="Z3" s="0" t="s">
         <x:v>244</x:v>
       </x:c>
-      <x:c r="V3" s="0" t="s">
+      <x:c r="AA3" s="0" t="s">
         <x:v>245</x:v>
-      </x:c>
-      <x:c r="W3" s="0" t="s">
-        <x:v>246</x:v>
-      </x:c>
-      <x:c r="X3" s="0" t="s">
-        <x:v>247</x:v>
-      </x:c>
-      <x:c r="Y3" s="0" t="s">
-        <x:v>248</x:v>
-      </x:c>
-      <x:c r="Z3" s="0" t="s">
-        <x:v>249</x:v>
-      </x:c>
-      <x:c r="AA3" s="0" t="s">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="AB3" s="0" t="s">
-        <x:v>251</x:v>
-      </x:c>
-      <x:c r="AC3" s="0" t="s">
-        <x:v>252</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2691,13 +2622,13 @@
           <x14:formula1>
             <xm:f>Lists!$G$2:$G$4</xm:f>
           </x14:formula1>
-          <xm:sqref>AB3:AB1000</xm:sqref>
+          <xm:sqref>Z3:Z1000</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="">
           <x14:formula1>
             <xm:f>Lists!$H$2:$H$5</xm:f>
           </x14:formula1>
-          <xm:sqref>AC3:AC1000</xm:sqref>
+          <xm:sqref>AA3:AA1000</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </x:ext>
@@ -2725,89 +2656,89 @@
   <x:sheetData>
     <x:row r="1" spans="1:9">
       <x:c r="A1" s="2" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="B1" s="2" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="C1" s="2" t="s">
         <x:v>182</x:v>
       </x:c>
-      <x:c r="B1" s="2" t="s">
-        <x:v>184</x:v>
-      </x:c>
-      <x:c r="C1" s="2" t="s">
-        <x:v>187</x:v>
-      </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>190</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="F1" s="2" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="G1" s="2" t="s">
         <x:v>193</x:v>
       </x:c>
-      <x:c r="F1" s="2" t="s">
-        <x:v>196</x:v>
-      </x:c>
-      <x:c r="G1" s="2" t="s">
+      <x:c r="H1" s="2" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="I1" s="2" t="s">
         <x:v>198</x:v>
-      </x:c>
-      <x:c r="H1" s="2" t="s">
-        <x:v>200</x:v>
-      </x:c>
-      <x:c r="I1" s="2" t="s">
-        <x:v>203</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:9" hidden="1">
       <x:c r="A2" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
         <x:v>183</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>185</x:v>
-      </x:c>
-      <x:c r="C2" s="0" t="s">
-        <x:v>188</x:v>
-      </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
         <x:v>194</x:v>
       </x:c>
-      <x:c r="F2" s="0" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="G2" s="0" t="s">
+      <x:c r="H2" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
         <x:v>199</x:v>
-      </x:c>
-      <x:c r="H2" s="0" t="s">
-        <x:v>201</x:v>
-      </x:c>
-      <x:c r="I2" s="0" t="s">
-        <x:v>204</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
       <x:c r="A3" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="D3" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="E3" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="F3" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
         <x:v>253</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
+      <x:c r="I3" s="0" t="s">
         <x:v>254</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>255</x:v>
-      </x:c>
-      <x:c r="D3" s="0" t="s">
-        <x:v>256</x:v>
-      </x:c>
-      <x:c r="E3" s="0" t="s">
-        <x:v>257</x:v>
-      </x:c>
-      <x:c r="F3" s="0" t="s">
-        <x:v>258</x:v>
-      </x:c>
-      <x:c r="G3" s="0" t="s">
-        <x:v>259</x:v>
-      </x:c>
-      <x:c r="H3" s="0" t="s">
-        <x:v>260</x:v>
-      </x:c>
-      <x:c r="I3" s="0" t="s">
-        <x:v>261</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/tools/Polhem.Definition.Spreadsheet/Templates/FormSchema.zh-TW.xlsx
+++ b/tools/Polhem.Definition.Spreadsheet/Templates/FormSchema.zh-TW.xlsx
@@ -537,6 +537,15 @@
     <x:t>DisplayFields</x:t>
   </x:si>
   <x:si>
+    <x:t>異動時回呼後端</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ValueChangeCallback</x:t>
+  </x:si>
+  <x:si>
+    <x:t>填 Y 時，值異動後由後端帶回相關欄位或驗證此值。</x:t>
+  </x:si>
+  <x:si>
     <x:t>語系列舉</x:t>
   </x:si>
   <x:si>
@@ -748,6 +757,9 @@
   </x:si>
   <x:si>
     <x:t>{{Fields.DisplayFields}}</x:t>
+  </x:si>
+  <x:si>
+    <x:t>{{Fields.ValueChangeCallback}}</x:t>
   </x:si>
   <x:si>
     <x:t>{{Fields.LangEnumName}}</x:t>
@@ -1188,7 +1200,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D65"/>
+  <x:dimension ref="A1:D66"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="12.710625" style="0" customWidth="1"/>
@@ -1846,7 +1858,7 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="55" spans="1:4">
@@ -1854,10 +1866,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
         <x:v>57</x:v>
@@ -1868,10 +1880,10 @@
         <x:v>115</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
         <x:v>57</x:v>
@@ -1879,13 +1891,13 @@
     </x:row>
     <x:row r="57" spans="1:4">
       <x:c r="A57" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
         <x:v>57</x:v>
@@ -1893,21 +1905,21 @@
     </x:row>
     <x:row r="58" spans="1:4">
       <x:c r="A58" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:4">
       <x:c r="A59" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
         <x:v>182</x:v>
@@ -1921,7 +1933,7 @@
     </x:row>
     <x:row r="60" spans="1:4">
       <x:c r="A60" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
         <x:v>185</x:v>
@@ -1935,7 +1947,7 @@
     </x:row>
     <x:row r="61" spans="1:4">
       <x:c r="A61" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
         <x:v>188</x:v>
@@ -1949,7 +1961,7 @@
     </x:row>
     <x:row r="62" spans="1:4">
       <x:c r="A62" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
         <x:v>191</x:v>
@@ -1958,18 +1970,18 @@
         <x:v>192</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>193</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:4">
       <x:c r="A63" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
         <x:v>57</x:v>
@@ -1977,21 +1989,21 @@
     </x:row>
     <x:row r="64" spans="1:4">
       <x:c r="A64" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>197</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:4">
       <x:c r="A65" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
         <x:v>198</x:v>
@@ -2000,6 +2012,20 @@
         <x:v>199</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:4">
+      <x:c r="A66" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
     </x:row>
@@ -2028,11 +2054,11 @@
   <x:sheetData>
     <x:row r="1" spans="1:4">
       <x:c r="A1" s="2" t="s">
-        <x:v>200</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="B1" s="2"/>
       <x:c r="C1" s="2" t="s">
-        <x:v>201</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
         <x:v>68</x:v>
@@ -2046,7 +2072,7 @@
         <x:v>71</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
         <x:v>72</x:v>
@@ -2060,7 +2086,7 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
         <x:v>75</x:v>
@@ -2074,7 +2100,7 @@
         <x:v>77</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
         <x:v>78</x:v>
@@ -2088,7 +2114,7 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
         <x:v>80</x:v>
@@ -2102,7 +2128,7 @@
         <x:v>82</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
         <x:v>83</x:v>
@@ -2116,7 +2142,7 @@
         <x:v>85</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
         <x:v>86</x:v>
@@ -2130,7 +2156,7 @@
         <x:v>88</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>208</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
         <x:v>89</x:v>
@@ -2144,7 +2170,7 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
         <x:v>92</x:v>
@@ -2158,7 +2184,7 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
         <x:v>95</x:v>
@@ -2172,7 +2198,7 @@
         <x:v>97</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
         <x:v>98</x:v>
@@ -2186,7 +2212,7 @@
         <x:v>100</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
         <x:v>101</x:v>
@@ -2200,7 +2226,7 @@
         <x:v>103</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
         <x:v>104</x:v>
@@ -2214,7 +2240,7 @@
         <x:v>106</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
         <x:v>107</x:v>
@@ -2283,16 +2309,16 @@
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>221</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2309,7 +2335,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:AA3"/>
+  <x:dimension ref="A1:AB3"/>
   <x:sheetFormatPr defaultRowHeight="15" outlineLevelCol="1"/>
   <x:cols>
     <x:col min="1" max="1" width="16.710625" style="0" customWidth="1"/>
@@ -2327,10 +2353,12 @@
     <x:col min="18" max="18" width="10.710625" style="0" customWidth="1"/>
     <x:col min="19" max="19" width="14.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
     <x:col min="20" max="20" width="24.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
-    <x:col min="21" max="27" width="14.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <x:col min="21" max="24" width="14.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <x:col min="25" max="25" width="8.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
+    <x:col min="26" max="28" width="14.710625" style="0" hidden="1" customWidth="1" outlineLevel="1" collapsed="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:27">
+    <x:row r="1" spans="1:28">
       <x:c r="A1" s="2" t="s">
         <x:v>116</x:v>
       </x:c>
@@ -2407,13 +2435,16 @@
         <x:v>172</x:v>
       </x:c>
       <x:c r="Z1" s="4" t="s">
-        <x:v>174</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="AA1" s="4" t="s">
-        <x:v>175</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" spans="1:27" hidden="1">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="AB1" s="4" t="s">
+        <x:v>178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:28" hidden="1">
       <x:c r="A2" s="0" t="s">
         <x:v>110</x:v>
       </x:c>
@@ -2490,93 +2521,99 @@
         <x:v>173</x:v>
       </x:c>
       <x:c r="Z2" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="AA2" s="0" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="AA2" s="0" t="s">
+      <x:c r="AB2" s="0" t="s">
         <x:v>51</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:27">
+    <x:row r="3" spans="1:28">
       <x:c r="A3" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="J3" s="0" t="s">
-        <x:v>228</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="K3" s="0" t="s">
-        <x:v>229</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>230</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
-        <x:v>231</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="N3" s="0" t="s">
-        <x:v>232</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="O3" s="0" t="s">
-        <x:v>233</x:v>
+        <x:v>236</x:v>
       </x:c>
       <x:c r="P3" s="0" t="s">
-        <x:v>234</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="Q3" s="0" t="s">
-        <x:v>235</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="R3" s="0" t="s">
-        <x:v>236</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="S3" s="0" t="s">
-        <x:v>237</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="T3" s="0" t="s">
-        <x:v>238</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="U3" s="0" t="s">
-        <x:v>239</x:v>
+        <x:v>242</x:v>
       </x:c>
       <x:c r="V3" s="0" t="s">
-        <x:v>240</x:v>
+        <x:v>243</x:v>
       </x:c>
       <x:c r="W3" s="0" t="s">
-        <x:v>241</x:v>
+        <x:v>244</x:v>
       </x:c>
       <x:c r="X3" s="0" t="s">
-        <x:v>242</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="Y3" s="0" t="s">
-        <x:v>243</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="Z3" s="0" t="s">
-        <x:v>244</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="AA3" s="0" t="s">
-        <x:v>245</x:v>
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="AB3" s="0" t="s">
+        <x:v>249</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2598,7 +2635,7 @@
           <x14:formula1>
             <xm:f>Lists!$A$2:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>G3:I1000</xm:sqref>
+          <xm:sqref>G3:I1000 Y3:Y1000</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="">
           <x14:formula1>
@@ -2622,13 +2659,13 @@
           <x14:formula1>
             <xm:f>Lists!$G$2:$G$4</xm:f>
           </x14:formula1>
-          <xm:sqref>Z3:Z1000</xm:sqref>
+          <xm:sqref>AA3:AA1000</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" errorStyle="stop" operator="between" allowBlank="1" showDropDown="0" showInputMessage="1" showErrorMessage="1" errorTitle="" error="" promptTitle="" prompt="">
           <x14:formula1>
             <xm:f>Lists!$H$2:$H$5</xm:f>
           </x14:formula1>
-          <xm:sqref>AA3:AA1000</xm:sqref>
+          <xm:sqref>AB3:AB1000</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </x:ext>
@@ -2656,89 +2693,89 @@
   <x:sheetData>
     <x:row r="1" spans="1:9">
       <x:c r="A1" s="2" t="s">
-        <x:v>177</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="B1" s="2" t="s">
-        <x:v>179</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
-        <x:v>182</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>185</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>188</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>191</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>193</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="H1" s="2" t="s">
-        <x:v>195</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="I1" s="2" t="s">
-        <x:v>198</x:v>
+        <x:v>201</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:9" hidden="1">
       <x:c r="A2" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
-        <x:v>194</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="H2" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="I2" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>202</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:9">
       <x:c r="A3" s="0" t="s">
-        <x:v>246</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>247</x:v>
+        <x:v>251</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>248</x:v>
+        <x:v>252</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>249</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>250</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>251</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
-        <x:v>252</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="H3" s="0" t="s">
-        <x:v>253</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="I3" s="0" t="s">
-        <x:v>254</x:v>
+        <x:v>258</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
